--- a/tame_output/ON/bt/strategyON_20240806.xlsx
+++ b/tame_output/ON/bt/strategyON_20240806.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>36.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.9%</t>
+          <t>451.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-671.2%</t>
+          <t>-673.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.8%</t>
+          <t>-153.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-195.5%</t>
+          <t>-194.4%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.0%</t>
+          <t>-131.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,16 +1400,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-55.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2046"/>
+  <dimension ref="A1:G2047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.616483965746217</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48619,6 +48619,29 @@
       </c>
       <c r="G2046" t="n">
         <v>3.886644085414567</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="2" t="n">
+        <v>45509</v>
+      </c>
+      <c r="B2047" t="n">
+        <v>3.646857607760313</v>
+      </c>
+      <c r="C2047" t="n">
+        <v>3.866180764699744</v>
+      </c>
+      <c r="D2047" t="n">
+        <v>-5.119396730320966</v>
+      </c>
+      <c r="E2047" t="n">
+        <v>1.818065648257611</v>
+      </c>
+      <c r="F2047" t="n">
+        <v>0.06777665148069478</v>
+      </c>
+      <c r="G2047" t="n">
+        <v>3.906846755588162</v>
       </c>
     </row>
   </sheetData>
